--- a/bin/rfc_information_types_source.xlsx
+++ b/bin/rfc_information_types_source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFSasso2\Work Folders\Documents\IQA\data call 2024\SURVEY RESULTS 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4E8BD5-7D44-42E8-8AE8-5DC24BC1E058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69382AD2-8C41-4CC2-98F1-2B074DD80845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
   </bookViews>
   <sheets>
     <sheet name="FY19" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="FY21" sheetId="11" r:id="rId3"/>
     <sheet name="FY22" sheetId="10" r:id="rId4"/>
     <sheet name="FY23" sheetId="13" r:id="rId5"/>
+    <sheet name="FY24" sheetId="14" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,10 +28,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="25">
   <si>
     <t>Agency</t>
   </si>
@@ -108,6 +109,12 @@
   <si>
     <t>USDA</t>
   </si>
+  <si>
+    <t>SEC</t>
+  </si>
+  <si>
+    <t>DOD</t>
+  </si>
 </sst>
 </file>
 
@@ -145,17 +152,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6508426B-287A-4A7A-B704-706E8CAADF1A}"/>
+    <cellStyle name="Normal_FY24" xfId="2" xr:uid="{A9EFA6C8-174E-4D54-B5E0-97CB870CFF05}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -171,9 +181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,7 +221,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -317,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -459,7 +469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -876,8 +886,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1300,8 +1318,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1722,8 +1748,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -2142,8 +2176,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -2566,8 +2608,296 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7377C4E-7C29-4AE4-8152-9A18B8E55C85}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/bin/rfc_information_types_source.xlsx
+++ b/bin/rfc_information_types_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69382AD2-8C41-4CC2-98F1-2B074DD80845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854DBBA4-205B-49D0-9064-7E5FC1E345D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
   </bookViews>
   <sheets>
     <sheet name="FY19" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="FY22" sheetId="10" r:id="rId4"/>
     <sheet name="FY23" sheetId="13" r:id="rId5"/>
     <sheet name="FY24" sheetId="14" r:id="rId6"/>
+    <sheet name="FY25" sheetId="15" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="26">
   <si>
     <t>Agency</t>
   </si>
@@ -114,6 +118,9 @@
   </si>
   <si>
     <t>DOD</t>
+  </si>
+  <si>
+    <t>DOT</t>
   </si>
 </sst>
 </file>
@@ -896,8 +903,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1328,8 +1339,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1758,8 +1773,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2186,8 +2205,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2618,8 +2641,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2898,8 +2925,307 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C6CE7B-C10E-4C64-83EE-56A047EDECA1}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
